--- a/data/trans_dic/P21B_R-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P21B_R-Estudios-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>97,15%</t>
+          <t>97,22%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>97,86%</t>
+          <t>97,72%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>97,59%</t>
+          <t>97,54%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>90,73; 97,26</t>
+          <t>90,07; 97,45</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>94,96; 99,2</t>
+          <t>95,46; 99,21</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>94,53; 99,41</t>
+          <t>94,66; 99,41</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>93,58; 98,93</t>
+          <t>93,89; 98,92</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>94,92; 98,64</t>
+          <t>95,34; 98,8</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,76; 99,56</t>
+          <t>97,19; 99,75</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>95,62; 99,56</t>
+          <t>95,3; 99,55</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>95,51; 99,03</t>
+          <t>95,2; 98,86</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>94,4; 97,73</t>
+          <t>94,32; 97,78</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>97,2; 99,25</t>
+          <t>97,07; 99,26</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>96,07; 99,3</t>
+          <t>96,36; 99,39</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>95,76; 98,67</t>
+          <t>95,73; 98,58</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>93,47%</t>
+          <t>93,13%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>93,96%</t>
+          <t>91,47%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>93,77%</t>
+          <t>92,23%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>94,9; 99,05</t>
+          <t>94,74; 99,03</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>95,17; 98,98</t>
+          <t>95,65; 98,98</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>88,93; 94,99</t>
+          <t>88,47; 95,16</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>89,31; 95,52</t>
+          <t>89,31; 95,43</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>94,7; 98,41</t>
+          <t>94,97; 98,47</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>95,24; 98,53</t>
+          <t>95,21; 98,51</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>91,32; 96,39</t>
+          <t>91,28; 96,43</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>90,35; 97,78</t>
+          <t>89,26; 93,93</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>95,69; 98,33</t>
+          <t>95,55; 98,25</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>96,01; 98,46</t>
+          <t>95,94; 98,37</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>91,12; 95,07</t>
+          <t>91,13; 95,05</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>91,64; 97,05</t>
+          <t>90,09; 93,93</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>79,79%</t>
+          <t>81,19%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>84,75%</t>
+          <t>84,62%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>82,52%</t>
+          <t>83,05%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>78,62; 95,18</t>
+          <t>79,66; 95,6</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>86,81; 98,61</t>
+          <t>85,78; 98,43</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>75,03; 92,5</t>
+          <t>74,99; 92,32</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>71,42; 86,04</t>
+          <t>73,28; 86,99</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>87,12; 97,78</t>
+          <t>86,96; 97,4</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>80,92; 93,74</t>
+          <t>80,72; 93,43</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>69,76; 85,44</t>
+          <t>70,15; 84,79</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>79,52; 89,15</t>
+          <t>78,93; 88,65</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>86,72; 95,58</t>
+          <t>86,92; 96,04</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>85,22; 94,46</t>
+          <t>84,5; 94,11</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>74,75; 86,61</t>
+          <t>75,1; 86,11</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>77,78; 86,42</t>
+          <t>78,78; 87,04</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>91,37%</t>
+          <t>91,32%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>93,27%</t>
+          <t>91,68%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>92,52%</t>
+          <t>91,52%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>93,33; 96,91</t>
+          <t>93,1; 96,98</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>95,81; 98,49</t>
+          <t>95,78; 98,44</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>90,2; 94,9</t>
+          <t>90,31; 94,88</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>88,48; 93,48</t>
+          <t>88,58; 93,41</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>95,29; 97,81</t>
+          <t>95,36; 97,81</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,66; 98,02</t>
+          <t>95,52; 97,86</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>90,1; 94,27</t>
+          <t>90,37; 94,44</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>91,04; 96,57</t>
+          <t>89,67; 93,21</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>95,04; 97,16</t>
+          <t>95,08; 97,2</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>96,16; 97,9</t>
+          <t>96,06; 97,87</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>90,95; 94,03</t>
+          <t>91,14; 94,04</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>90,95; 95,22</t>
+          <t>90,04; 92,96</t>
         </is>
       </c>
     </row>
@@ -1451,7 +1451,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>128465</t>
+          <t>136883</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>214286</t>
+          <t>234214</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>342750</t>
+          <t>371096</t>
         </is>
       </c>
     </row>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>179448; 192371</t>
+          <t>178138; 192746</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>237306; 247903</t>
+          <t>238549; 247930</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>129696; 136398</t>
+          <t>129874; 136398</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>123743; 130816</t>
+          <t>132199; 139279</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>324138; 336841</t>
+          <t>325570; 337373</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>396538; 407999</t>
+          <t>398299; 408764</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>213360; 222158</t>
+          <t>212658; 222135</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>209137; 216843</t>
+          <t>228172; 236947</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>509029; 526986</t>
+          <t>508600; 527257</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>641233; 654763</t>
+          <t>640370; 654846</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>346201; 357832</t>
+          <t>347243; 358165</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>336328; 346532</t>
+          <t>364228; 375064</t>
         </is>
       </c>
     </row>
@@ -1659,7 +1659,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>377503</t>
+          <t>401836</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1679,7 +1679,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>615381</t>
+          <t>460092</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>992884</t>
+          <t>861928</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>266714; 278371</t>
+          <t>266276; 278340</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>364972; 379580</t>
+          <t>366825; 379611</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>299324; 319727</t>
+          <t>297778; 320311</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>360665; 385758</t>
+          <t>385353; 411754</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>356504; 370446</t>
+          <t>357530; 370671</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>429574; 444429</t>
+          <t>429443; 444338</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>353921; 373588</t>
+          <t>353760; 373751</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>591716; 640427</t>
+          <t>448983; 472483</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>629143; 646526</t>
+          <t>628250; 645980</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>801307; 821739</t>
+          <t>800652; 820962</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>659835; 688461</t>
+          <t>659906; 688340</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>970300; 1027592</t>
+          <t>841905; 877757</t>
         </is>
       </c>
     </row>
@@ -1867,7 +1867,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>111243</t>
+          <t>129349</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>145067</t>
+          <t>160851</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>256310</t>
+          <t>290201</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>62588; 75771</t>
+          <t>63412; 76108</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>60303; 68499</t>
+          <t>59588; 68377</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>55444; 68349</t>
+          <t>55409; 68220</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>99578; 119952</t>
+          <t>116753; 138587</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>92433; 103739</t>
+          <t>92260; 103338</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>92504; 107154</t>
+          <t>92273; 106802</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>93641; 114684</t>
+          <t>94157; 113816</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>136126; 152599</t>
+          <t>150038; 168517</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>161050; 177497</t>
+          <t>161407; 178358</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>156611; 173589</t>
+          <t>155283; 172945</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>155577; 180264</t>
+          <t>156305; 179210</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>241595; 268432</t>
+          <t>275250; 304132</t>
         </is>
       </c>
     </row>
@@ -2075,7 +2075,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>617211</t>
+          <t>668069</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2095,7 +2095,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>974734</t>
+          <t>855157</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>1591945</t>
+          <t>1523226</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>521171; 541164</t>
+          <t>519926; 541582</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>673390; 692227</t>
+          <t>673245; 691889</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>494000; 519775</t>
+          <t>494650; 519661</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>597694; 631440</t>
+          <t>648046; 683416</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>785172; 805944</t>
+          <t>785811; 805989</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>932827; 955854</t>
+          <t>931445; 954278</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>671202; 702276</t>
+          <t>673215; 703523</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>951452; 1009206</t>
+          <t>836447; 869409</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1313868; 1343182</t>
+          <t>1314420; 1343697</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1613597; 1642869</t>
+          <t>1611962; 1642247</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1175718; 1215512</t>
+          <t>1178142; 1215608</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>1564921; 1638438</t>
+          <t>1498524; 1547281</t>
         </is>
       </c>
     </row>
